--- a/Excel/wos.xlsx
+++ b/Excel/wos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\auto\itemAndQty\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\auto\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDC6072-D1EA-46D7-ADCC-427E9C75BDA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B12360-7503-4599-984D-73E030E9AE6F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{DFCD4857-F2CC-45E7-A45D-BCDB90E6391F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
   <si>
     <t>EA</t>
   </si>
@@ -54,100 +54,217 @@
     <t>WO#</t>
   </si>
   <si>
-    <t>VX IT 5309</t>
-  </si>
-  <si>
-    <t>19" Rack 42RU, 800x1000mm</t>
-  </si>
-  <si>
-    <t>PRECISION-7960-RACK</t>
-  </si>
-  <si>
-    <t>Configuration PC (19" 2RU Rack</t>
-  </si>
-  <si>
-    <t>OPTIPLEX-TOWER</t>
-  </si>
-  <si>
-    <t>Operator Workstation PC, Intel</t>
-  </si>
-  <si>
-    <t>P2725H</t>
-  </si>
-  <si>
-    <t>Dell Monitor 27 inch TFT</t>
-  </si>
-  <si>
-    <t>ARU2-CON</t>
-  </si>
-  <si>
-    <t>KVM Extender Receiver, Display</t>
-  </si>
-  <si>
-    <t>ARU2-CPU</t>
-  </si>
-  <si>
-    <t>KVM Extender Transmitter, Disp</t>
-  </si>
-  <si>
-    <t>17HR-UK-USB</t>
-  </si>
-  <si>
-    <t>KVM 19" rack-mountable Display</t>
-  </si>
-  <si>
-    <t>CS 19208</t>
-  </si>
-  <si>
-    <t>KVM Switch</t>
-  </si>
-  <si>
-    <t>ECLIPSE-HX-DELTA-16P</t>
-  </si>
-  <si>
-    <t>Eclipse Intercom Frame, 4 card</t>
-  </si>
-  <si>
-    <t>E-IPA-32-HX</t>
-  </si>
-  <si>
-    <t>IP Matrix Card for HX Frame</t>
-  </si>
-  <si>
-    <t>V12RDDX4</t>
-  </si>
-  <si>
-    <t>Intercom Panel V-5eries, 12 ke</t>
-  </si>
-  <si>
-    <t>110/340</t>
-  </si>
-  <si>
-    <t>Gooseneck Microphone for Inter</t>
-  </si>
-  <si>
-    <t>VT-PNLB-12R-X4</t>
-  </si>
-  <si>
-    <t>Intercom Panel V-Series, 12 ke</t>
-  </si>
-  <si>
-    <t>CC-110-X4</t>
-  </si>
-  <si>
-    <t>Headset Single Ear, XLR(f) 4pi</t>
-  </si>
-  <si>
-    <t>ARCADIA-X4-16P</t>
-  </si>
-  <si>
-    <t>HelixNet Masterstation, IP con</t>
-  </si>
-  <si>
-    <t>HXII-BP-X4</t>
-  </si>
-  <si>
-    <t>HelixNet Beltpack</t>
+    <t>SPLHC63 25M</t>
+  </si>
+  <si>
+    <t>Liquid Tight Flexible Conduit,</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>LT206</t>
+  </si>
+  <si>
+    <t>Connector, Straight, 2", Die C</t>
+  </si>
+  <si>
+    <t>DTC4</t>
+  </si>
+  <si>
+    <t>Telescopic Coupler 32mm</t>
+  </si>
+  <si>
+    <t>004E8J-EG115EYL</t>
+  </si>
+  <si>
+    <t>Corning Fiber Optic Cables</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>ZA08WKF01- A1000</t>
+  </si>
+  <si>
+    <t>Belden Cable</t>
+  </si>
+  <si>
+    <t>ZA08WKF01-X1000</t>
+  </si>
+  <si>
+    <t>8.0C-H6A-D1-IR</t>
+  </si>
+  <si>
+    <t>IR Dome Camera</t>
+  </si>
+  <si>
+    <t>CCXFCB-L0047-C002-L7</t>
+  </si>
+  <si>
+    <t>S/FTP 1200/22 A-XR, 4P, LS0H-3</t>
+  </si>
+  <si>
+    <t>GNA_F_00304511</t>
+  </si>
+  <si>
+    <t>HDG TRUNKING 50X50X1.5X3000 MM</t>
+  </si>
+  <si>
+    <t>GNA_F_00607697</t>
+  </si>
+  <si>
+    <t>Cable Trunking Angle</t>
+  </si>
+  <si>
+    <t>SPLHC32 25M</t>
+  </si>
+  <si>
+    <t>SPIT-58585-</t>
+  </si>
+  <si>
+    <t>SPIT STEEL ANCHOR - GRIP L M10</t>
+  </si>
+  <si>
+    <t>TOP-DUCT TAPE</t>
+  </si>
+  <si>
+    <t>Duct Tape, 2"</t>
+  </si>
+  <si>
+    <t>CE00100</t>
+  </si>
+  <si>
+    <t>EMT Conduit 1 inch</t>
+  </si>
+  <si>
+    <t>USC100</t>
+  </si>
+  <si>
+    <t>Universal Strut Clamp, 1 Inch</t>
+  </si>
+  <si>
+    <t>Hammer-set Anchor with Screw</t>
+  </si>
+  <si>
+    <t>03-1605-00081</t>
+  </si>
+  <si>
+    <t>In/Out LSZH dielectric armored</t>
+  </si>
+  <si>
+    <t>H51-032-01-WH</t>
+  </si>
+  <si>
+    <t>Wall Mounting Kit (White)</t>
+  </si>
+  <si>
+    <t>OLFLEX CLASSIC 110 Black</t>
+  </si>
+  <si>
+    <t>OLFLEX CLASSIC 110 CY BK</t>
+  </si>
+  <si>
+    <t>CUSTFLRBX</t>
+  </si>
+  <si>
+    <t>Customized Floorbox Inlet Out</t>
+  </si>
+  <si>
+    <t>AVATUS-C-36</t>
+  </si>
+  <si>
+    <t>AVATUS Control Surface 36 Face</t>
+  </si>
+  <si>
+    <t>CUSTOM ENCLOSURE</t>
+  </si>
+  <si>
+    <t>Customized Enclosure</t>
+  </si>
+  <si>
+    <t>H51-035-00</t>
+  </si>
+  <si>
+    <t>IP55 Kit</t>
+  </si>
+  <si>
+    <t>040402G5Z20003M</t>
+  </si>
+  <si>
+    <t>FO-Patchcord Assembly Duplex 3</t>
+  </si>
+  <si>
+    <t>CCAAGB-G1002-A015-C0</t>
+  </si>
+  <si>
+    <t>S/FTP FLEX/26,CAT.6A,GY,2XRJ45</t>
+  </si>
+  <si>
+    <t>CCAAGB-G1002-A020-C0</t>
+  </si>
+  <si>
+    <t>Corning</t>
+  </si>
+  <si>
+    <t>RAL 7035 WHD 800x20</t>
+  </si>
+  <si>
+    <t>Side panel, screw-fastened</t>
+  </si>
+  <si>
+    <t>Fan mounting plate</t>
+  </si>
+  <si>
+    <t>DK Fan expansion kit</t>
+  </si>
+  <si>
+    <t>SM Connection cable, For power</t>
+  </si>
+  <si>
+    <t>IT Cable duct</t>
+  </si>
+  <si>
+    <t>GENELEC 8050BPM</t>
+  </si>
+  <si>
+    <t>2-Way Active Studio Monitor</t>
+  </si>
+  <si>
+    <t>8000-402B</t>
+  </si>
+  <si>
+    <t>Wall Mount, Black</t>
+  </si>
+  <si>
+    <t>9001AP</t>
+  </si>
+  <si>
+    <t>Volume Control</t>
+  </si>
+  <si>
+    <t>SFP28-25G-LR</t>
+  </si>
+  <si>
+    <t>Dell 0YR96 25Gb FC Long Range</t>
+  </si>
+  <si>
+    <t>DCV6</t>
+  </si>
+  <si>
+    <t>PVC Conduit 2 inch (50 mm)</t>
+  </si>
+  <si>
+    <t>DHB6</t>
+  </si>
+  <si>
+    <t>PVC Elbow 2 inch (50 mm)</t>
+  </si>
+  <si>
+    <t>DNC6</t>
+  </si>
+  <si>
+    <t>PVC Coupling 2 inch (50 mm)</t>
   </si>
 </sst>
 </file>
@@ -202,7 +319,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -239,7 +356,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -253,7 +381,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right style="double">
         <color indexed="64"/>
       </right>
       <top/>
@@ -262,48 +390,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -314,31 +405,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -655,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D27B97C-6AC3-486F-A4C6-441F548ECEA7}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="135.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -695,368 +774,943 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9">
-        <v>28556.36</v>
+      <c r="C2" s="4">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7">
+        <v>3050</v>
       </c>
       <c r="G2" s="8">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
+      <c r="A3" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11">
-        <v>53439.91</v>
-      </c>
-      <c r="G3" s="4">
-        <v>346</v>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>41.5</v>
+      </c>
+      <c r="G3" s="8">
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="10" t="s">
-        <v>13</v>
+      <c r="A4" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4">
-        <v>2</v>
+        <v>504</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11">
-        <v>7101.9</v>
-      </c>
-      <c r="G4" s="4">
-        <v>346</v>
+      <c r="E4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="G4" s="8">
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="10" t="s">
-        <v>15</v>
+      <c r="A5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4">
-        <v>2</v>
+        <v>78370</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11">
-        <v>1517.17</v>
-      </c>
-      <c r="G5" s="4">
-        <v>346</v>
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.9236</v>
+      </c>
+      <c r="G5" s="8">
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A6" s="10" t="s">
-        <v>17</v>
+      <c r="A6" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4">
+        <v>22000</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4">
-        <v>2</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11">
-        <v>17550.490000000002</v>
-      </c>
-      <c r="G6" s="4">
-        <v>346</v>
+      <c r="E6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="8">
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A7" s="10" t="s">
-        <v>19</v>
+      <c r="A7" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C7" s="4">
-        <v>2</v>
+        <v>9940</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11">
-        <v>17873.13</v>
-      </c>
-      <c r="G7" s="4">
-        <v>346</v>
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A8" s="10" t="s">
-        <v>21</v>
+      <c r="A8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11">
-        <v>17972.39</v>
-      </c>
-      <c r="G8" s="4">
-        <v>346</v>
+      <c r="E8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>2779.99</v>
+      </c>
+      <c r="G8" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="10" t="s">
-        <v>23</v>
+      <c r="A9" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="11">
-        <v>7262.17</v>
-      </c>
-      <c r="G9" s="4">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A10" s="10" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>4.6550000000000002</v>
+      </c>
+      <c r="G9" s="8">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30.75" thickBot="1">
+      <c r="A10" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11">
-        <v>103919.79</v>
-      </c>
-      <c r="G10" s="4">
-        <v>346</v>
+      <c r="E10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>77.013300000000001</v>
+      </c>
+      <c r="G10" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A11" s="10" t="s">
-        <v>27</v>
+      <c r="A11" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="11">
-        <v>61642.400000000001</v>
-      </c>
-      <c r="G11" s="4">
-        <v>346</v>
+      <c r="E11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>40.943800000000003</v>
+      </c>
+      <c r="G11" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A12" s="10" t="s">
-        <v>29</v>
+      <c r="A12" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="11">
-        <v>15740.69</v>
-      </c>
-      <c r="G12" s="4">
-        <v>346</v>
+      <c r="E12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1351.73</v>
+      </c>
+      <c r="G12" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="4">
-        <v>23</v>
+        <v>2000</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="11">
-        <v>1355.3</v>
-      </c>
-      <c r="G13" s="4">
-        <v>346</v>
+      <c r="E13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="G13" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="4">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="11">
-        <v>17036.52</v>
-      </c>
-      <c r="G14" s="4">
-        <v>346</v>
+      <c r="E14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="G14" s="8">
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="4">
-        <v>77</v>
+        <v>1016</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="11">
-        <v>1335.97</v>
-      </c>
-      <c r="G15" s="4">
-        <v>346</v>
+      <c r="E15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>20.000900000000001</v>
+      </c>
+      <c r="G15" s="8">
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G16" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="G17" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A18" s="6">
+        <v>60090</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.68459999999999999</v>
+      </c>
+      <c r="G18" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>15.0951</v>
+      </c>
+      <c r="G19" s="8">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11">
-        <v>54969.79</v>
-      </c>
-      <c r="G16" s="4">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="D20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A21" s="6">
+        <v>1120343</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>17.38</v>
+      </c>
+      <c r="G21" s="8">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A22" s="6">
+        <v>1121342</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>27.84</v>
+      </c>
+      <c r="G22" s="8">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="4">
+        <v>9</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7">
+        <v>14868.63</v>
+      </c>
+      <c r="G23" s="8">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7">
+        <v>289146.2</v>
+      </c>
+      <c r="G24" s="8">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="4">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7">
+        <v>7074.18</v>
+      </c>
+      <c r="G25" s="8">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="4">
+        <v>303</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>48.297600000000003</v>
+      </c>
+      <c r="G27" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="4">
+        <v>82</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>24</v>
+      </c>
+      <c r="G28" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="4">
+        <v>97</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>27</v>
+      </c>
+      <c r="G29" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A30" s="6">
+        <v>5307114</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7">
+        <v>6058.94</v>
+      </c>
+      <c r="G30" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A31" s="6">
+        <v>8108245</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4">
+        <v>759.19719999999995</v>
+      </c>
+      <c r="G31" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A32" s="6">
+        <v>5503020</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>956.99189999999999</v>
+      </c>
+      <c r="G32" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A33" s="6">
+        <v>7990000</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
+        <v>173.67080000000001</v>
+      </c>
+      <c r="G33" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A34" s="6">
+        <v>6450060</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>33.401600000000002</v>
+      </c>
+      <c r="G34" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A35" s="6">
+        <v>5302052</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>572.79650000000004</v>
+      </c>
+      <c r="G35" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="4">
+        <v>12</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="7">
+        <v>4543.62</v>
+      </c>
+      <c r="G36" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="4">
+        <v>12</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>414.42099999999999</v>
+      </c>
+      <c r="G37" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A38" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="4">
+        <v>12</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>408.32209999999998</v>
+      </c>
+      <c r="G38" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="4">
         <v>40</v>
       </c>
-      <c r="C17" s="4">
-        <v>54</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11">
-        <v>5573.14</v>
-      </c>
-      <c r="G17" s="12">
-        <v>346</v>
+      <c r="D39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="7">
+        <v>1615.08</v>
+      </c>
+      <c r="G39" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="4">
+        <v>500</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>13.45</v>
+      </c>
+      <c r="G40" s="8">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="4">
+        <v>200</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>8.6538000000000004</v>
+      </c>
+      <c r="G41" s="8">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="4">
+        <v>200</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1.41</v>
+      </c>
+      <c r="G42" s="8">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
